--- a/Project_ETF/ETF_Investment_Portfolio/009805/ETF_Investment_Portfolio_20260811.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/009805/ETF_Investment_Portfolio_20260811.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D71"/>
+  <dimension ref="A1:D72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24.75" customWidth="1" min="1" max="1"/>
@@ -616,7 +616,7 @@
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>11.46%</t>
+          <t>11.57%</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>10.58%</t>
+          <t>10.57%</t>
         </is>
       </c>
     </row>
@@ -655,12 +655,12 @@
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>88,025</t>
+          <t>88,425</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>8.04%</t>
+          <t>8.24%</t>
         </is>
       </c>
     </row>
@@ -677,12 +677,12 @@
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>34,655</t>
+          <t>34,755</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>7.74%</t>
+          <t>7.71%</t>
         </is>
       </c>
     </row>
@@ -699,12 +699,12 @@
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>190,256</t>
+          <t>191,056</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>5.45%</t>
+          <t>5.42%</t>
         </is>
       </c>
     </row>
@@ -721,56 +721,56 @@
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>101,191</t>
+          <t>101,591</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>4.15%</t>
+          <t>4.14%</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>BE UN</t>
+          <t>SO US</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>Bloom Energy Corp</t>
+          <t>南方公司</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>47,795</t>
+          <t>110,166</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>3.40%</t>
+          <t>3.35%</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>SO US</t>
+          <t>BE UN</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>南方公司</t>
+          <t>Bloom Energy Corp</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>109,766</t>
+          <t>47,895</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>3.39%</t>
+          <t>3.34%</t>
         </is>
       </c>
     </row>
@@ -787,12 +787,12 @@
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>18,879</t>
+          <t>18,979</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>3.22%</t>
+          <t>3.26%</t>
         </is>
       </c>
     </row>
@@ -809,12 +809,12 @@
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>57,459</t>
+          <t>57,659</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>3.15%</t>
+          <t>3.19%</t>
         </is>
       </c>
     </row>
@@ -831,12 +831,12 @@
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>114,183</t>
+          <t>114,583</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>2.59%</t>
+          <t>2.58%</t>
         </is>
       </c>
     </row>
@@ -853,12 +853,12 @@
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>52,827</t>
+          <t>53,027</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>2.19%</t>
+          <t>2.17%</t>
         </is>
       </c>
     </row>
@@ -875,12 +875,12 @@
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>21,931</t>
+          <t>22,031</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>2.00%</t>
+          <t>2.03%</t>
         </is>
       </c>
     </row>
@@ -897,12 +897,12 @@
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>132,901</t>
+          <t>133,501</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>2.00%</t>
+          <t>1.98%</t>
         </is>
       </c>
     </row>
@@ -919,12 +919,12 @@
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>23,704</t>
+          <t>23,804</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>1.92%</t>
+          <t>1.90%</t>
         </is>
       </c>
     </row>
@@ -941,12 +941,12 @@
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>60,703</t>
+          <t>61,003</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>1.58%</t>
+          <t>1.57%</t>
         </is>
       </c>
     </row>
@@ -963,12 +963,12 @@
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>35,880</t>
+          <t>35,980</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>1.29%</t>
+          <t>1.28%</t>
         </is>
       </c>
     </row>
@@ -985,12 +985,12 @@
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>48,536</t>
+          <t>48,636</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>1.22%</t>
+          <t>1.21%</t>
         </is>
       </c>
     </row>
@@ -1007,166 +1007,166 @@
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>75,101</t>
+          <t>75,401</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>1.19%</t>
+          <t>1.17%</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>ES US</t>
+          <t>EIX US</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>Eversource能源</t>
+          <t>愛迪生國際</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>48,760</t>
+          <t>50,110</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>1.17%</t>
+          <t>1.16%</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>EIX US</t>
+          <t>ES US</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>愛迪生國際</t>
+          <t>Eversource能源</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>49,910</t>
+          <t>48,960</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>1.14%</t>
+          <t>1.15%</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>ACM UN</t>
+          <t>WEC US</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>艾奕康</t>
+          <t>WEC能源集團公司</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>45,827</t>
+          <t>31,810</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>1.14%</t>
+          <t>1.12%</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>WEC US</t>
+          <t>TTEK UW</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>WEC能源集團公司</t>
+          <t>德照科技公司</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>31,710</t>
+          <t>93,063</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>1.14%</t>
+          <t>1.09%</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>TTEK UW</t>
+          <t>ETR US</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>德照科技公司</t>
+          <t>安特吉公司</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>92,663</t>
+          <t>29,745</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>1.10%</t>
+          <t>1.05%</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>ETR US</t>
+          <t>VST US</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>安特吉公司</t>
+          <t>維斯達能源公司</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>29,645</t>
+          <t>21,758</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>1.06%</t>
+          <t>1.04%</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>VST US</t>
+          <t>ACM UN</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>維斯達能源公司</t>
+          <t>艾奕康</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>21,658</t>
+          <t>46,027</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>1.05%</t>
+          <t>1.02%</t>
         </is>
       </c>
     </row>
@@ -1188,7 +1188,7 @@
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>1.00%</t>
+          <t>0.99%</t>
         </is>
       </c>
     </row>
@@ -1205,29 +1205,29 @@
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>26,869</t>
+          <t>26,969</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>0.97%</t>
+          <t>0.96%</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>AGX US</t>
+          <t>AEIS US</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>阿根公司</t>
+          <t>艾儀有限公司</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>4,821</t>
+          <t>8,804</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
@@ -1239,44 +1239,44 @@
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>AEIS US</t>
+          <t>DTE US</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>艾儀有限公司</t>
+          <t>DTE能源</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>8,804</t>
+          <t>20,209</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>0.94%</t>
+          <t>0.92%</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>DTE US</t>
+          <t>AGX US</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>DTE能源</t>
+          <t>阿根公司</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>20,209</t>
+          <t>4,821</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>0.93%</t>
+          <t>0.92%</t>
         </is>
       </c>
     </row>
@@ -1293,12 +1293,12 @@
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>73,174</t>
+          <t>73,474</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>0.87%</t>
+          <t>0.86%</t>
         </is>
       </c>
     </row>
@@ -1315,7 +1315,7 @@
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>142,245</t>
+          <t>142,945</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
@@ -1327,44 +1327,44 @@
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>EVRG US</t>
+          <t>ENS US</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>Evergy公司</t>
+          <t>EnerSys</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>29,514</t>
+          <t>12,952</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t>0.82%</t>
+          <t>0.80%</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>ENS US</t>
+          <t>EVRG US</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>EnerSys</t>
+          <t>Evergy公司</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>12,952</t>
+          <t>29,614</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>0.82%</t>
+          <t>0.80%</t>
         </is>
       </c>
     </row>
@@ -1386,7 +1386,7 @@
       </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t>0.79%</t>
+          <t>0.77%</t>
         </is>
       </c>
     </row>
@@ -1408,7 +1408,7 @@
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>0.72%</t>
+          <t>0.74%</t>
         </is>
       </c>
     </row>
@@ -1425,51 +1425,51 @@
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>29,891</t>
+          <t>29,991</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
         <is>
-          <t>0.70%</t>
+          <t>0.69%</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>LNT US</t>
+          <t>CNP US</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>聯合能源公司</t>
+          <t>Centerpoint能源</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>25,181</t>
+          <t>42,583</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>0.58%</t>
+          <t>0.57%</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>CNP US</t>
+          <t>LNT US</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>Centerpoint能源</t>
+          <t>聯合能源公司</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>42,383</t>
+          <t>25,181</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
@@ -1481,44 +1481,44 @@
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>NRG US</t>
+          <t>PNW US</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>NRG Energy Inc</t>
+          <t>皮那可資本公司</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>13,124</t>
+          <t>15,727</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>0.53%</t>
+          <t>0.52%</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>PNW US</t>
+          <t>NRG US</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>皮那可資本公司</t>
+          <t>NRG Energy Inc</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>15,727</t>
+          <t>13,124</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
         <is>
-          <t>0.53%</t>
+          <t>0.52%</t>
         </is>
       </c>
     </row>
@@ -1557,12 +1557,12 @@
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>92,102</t>
+          <t>92,502</t>
         </is>
       </c>
       <c r="D64" s="4" t="inlineStr">
         <is>
-          <t>0.46%</t>
+          <t>0.45%</t>
         </is>
       </c>
     </row>
@@ -1584,7 +1584,7 @@
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>0.41%</t>
+          <t>0.40%</t>
         </is>
       </c>
     </row>
@@ -1606,7 +1606,7 @@
       </c>
       <c r="D66" s="4" t="inlineStr">
         <is>
-          <t>0.40%</t>
+          <t>0.39%</t>
         </is>
       </c>
     </row>
@@ -1623,7 +1623,7 @@
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>22,919</t>
+          <t>23,019</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
@@ -1689,7 +1689,7 @@
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t>17,953</t>
+          <t>18,053</t>
         </is>
       </c>
       <c r="D70" s="4" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>37,261</t>
+          <t>37,461</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr">
@@ -1719,6 +1719,20 @@
           <t>0.01%</t>
         </is>
       </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="3" t="inlineStr">
+        <is>
+          <t>C_NTD</t>
+        </is>
+      </c>
+      <c r="B72" s="3" t="inlineStr"/>
+      <c r="C72" s="4" t="inlineStr">
+        <is>
+          <t>141,836,297</t>
+        </is>
+      </c>
+      <c r="D72" s="4" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="5">
